--- a/ig/mc-add-profils-dp/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:21:34+00:00</t>
+    <t>2023-05-17T18:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:27:08+00:00</t>
+    <t>2023-05-23T08:43:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil créé à partir de as-practitionerrole dans le contexte des données en libre accès.</t>
+    <t>Profil applicatif créé à partir du profil générique as-practitionerrole dans le contexte des données en libre accès de l’Annuaire Santé.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-dp-practitionerrole.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-dp-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T08:43:56+00:00</t>
+    <t>2023-05-23T08:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
